--- a/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">c8dc29a766acf8868fc9706a64afd79a56c4194d</t>
+          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
         </is>
       </c>
     </row>
@@ -90,7 +90,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 00:52:12</t>
+          <t xml:space="preserve">2026-08-27 01:07:32</t>
         </is>
       </c>
     </row>
@@ -800,17 +800,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">متطلبات النطاق التي ظهرت في دفتر رحلة موجة</t>
+          <t xml:space="preserve">لا اداة تنسب التغطية الالية الى نطاق - ولا دفتر رحلة يحمل معرف متطلب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">كل متطلبات النطاق في سجل المتطلبات</t>
+          <t xml:space="preserve">لا مقام - غير مقيس · والمقيس الحقيقي محطات الرحلات مطبوع في سبب كل صف</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">تقيس التغطية الالية وحدها - والقبول البشري محور مستقل</t>
+          <t xml:space="preserve">غير مقيس باعلان: التغطية الالية قائمة بمحطاتها ولكنها لا تنسب الى نطاق - والقبول البشري محور مستقل عنها</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 67054 محطة عابرة من 67368 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETB-c8dc29a7-20260827-005212</t>
+          <t xml:space="preserve">ETB-f8b6da6a-20260827-010731</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">c8dc29a766acf8868fc9706a64afd79a56c4194d</t>
+          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 03:52:12</t>
+          <t xml:space="preserve">2026-08-27 04:07:31</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
+          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
         </is>
       </c>
     </row>
@@ -90,7 +90,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:07:32</t>
+          <t xml:space="preserve">2026-08-27 01:16:52</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 68479 محطة عابرة من 68793 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETB-f8b6da6a-20260827-010731</t>
+          <t xml:space="preserve">ETB-47577ee7-20260827-011651</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">f8b6da6ab5a24d3dabb6ae943a2a808955d66f3d</t>
+          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:07:31</t>
+          <t xml:space="preserve">2026-08-27 04:16:51</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
+          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
         </is>
       </c>
     </row>
@@ -90,7 +90,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:16:52</t>
+          <t xml:space="preserve">2026-08-27 01:26:17</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 69334 محطة عابرة من 69648 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>

--- a/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
+++ b/docs/REPAIR01_20260823/baseline_v1/12 · مراجعة القيادة.xlsx
@@ -78,7 +78,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">9082e8cbf7d2c1288ba7458b99cf6b87a373d5ad</t>
+          <t xml:space="preserve">05a0010b03fa63f30746693f8d0975301b1d7e49</t>
         </is>
       </c>
     </row>
@@ -90,7 +90,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 01:26:17</t>
+          <t xml:space="preserve">2026-08-27 01:31:08</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7532,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70413 محطة عابرة من 70727 ولكنها لا تنسب الى نطاق</t>
+          <t xml:space="preserve">غير مقيس بحبة المتطلب: لا دفتر رحلة من 13 يحمل معرف متطلب - والتغطية الالية قائمة: 70698 محطة عابرة من 71012 ولكنها لا تنسب الى نطاق</t>
         </is>
       </c>
     </row>
@@ -8315,7 +8315,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETB-47577ee7-20260827-011651</t>
+          <t xml:space="preserve">ETB-5c186484-20260827-013107</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SNAP-02224261-20260827-145545</t>
+          <t xml:space="preserve">SNAP-5c186484-20260827-042001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">47577ee7f22d84fa3868337c2947b5e84db11951</t>
+          <t xml:space="preserve">5c18648431f48ca3d5591307ad301a00c57b4f7a</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -8365,7 +8365,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-27 04:16:51</t>
+          <t xml:space="preserve">2026-08-27 04:31:07</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
